--- a/exclusive_zone_groups.xlsx
+++ b/exclusive_zone_groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hprpln.sharepoint.com/sites/Hyperplanners/Documents partages/2. Product/Consuelo/Templates secto/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victoria/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{5799324B-DAB1-B741-9F3B-C5928CF11A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43EFEF36-8539-D146-A928-C4174BCAE38D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6DD1D4-0E12-0A44-A585-3EC0F2665873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="500" windowWidth="27900" windowHeight="16040" activeTab="1" xr2:uid="{03A70420-2429-4913-AA09-83D42AAD96D5}"/>
+    <workbookView xWindow="900" yWindow="500" windowWidth="27900" windowHeight="16040" xr2:uid="{03A70420-2429-4913-AA09-83D42AAD96D5}"/>
   </bookViews>
   <sheets>
     <sheet name="A compléter" sheetId="23" r:id="rId1"/>
@@ -393,10 +393,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -756,10 +756,10 @@
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="2" t="s">
         <v>1</v>
       </c>
@@ -771,7 +771,7 @@
       <c r="C9" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>43</v>
       </c>
     </row>
@@ -807,10 +807,10 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="4" t="s">
         <v>35</v>
       </c>
@@ -1014,6 +1014,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009FDD8E3FE5876F4E813B2FAE82B41E03" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="cb12b29134862a5551f6c1afe8cc1c27">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82" xmlns:ns3="c343035a-eeff-4647-bb36-aa636a1a9180" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a7f20c03ce02b47dd9895f5ff8ceaf6c" ns2:_="" ns3:_="">
     <xsd:import namespace="f8fd78c8-cd58-4647-bdeb-fdcf2106eb82"/>
@@ -1248,15 +1257,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE50D0AF-0036-48BA-B036-9BEEB417012E}">
   <ds:schemaRefs>
@@ -1275,6 +1275,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8885907-55A8-461B-8EC8-E298CEBCC84E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE0C152-A899-40D5-9FD0-0940F8D80769}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1291,12 +1299,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8885907-55A8-461B-8EC8-E298CEBCC84E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>